--- a/data/curated/moex/endpoints_probe/20260216/RU0002868001.xlsx
+++ b/data/curated/moex/endpoints_probe/20260216/RU0002868001.xlsx
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>380</v>
+        <v>768</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=be4a0860.64aee0c429869; path=/; expires=Mon, 16-Mar-26 10:02:08 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=f1fffdaf.64aeea5ef59b2; path=/; expires=Mon, 16-Mar-26 10:45:06 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>8725</v>
       </c>
       <c r="C2" t="n">
-        <v>20260216130205</v>
+        <v>20260216134505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=90", "Content-Type": "text/html", "Server": "nginx", "Set-Cookie": "MPTrack=68761f77.64aee0c6de416; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=871792d5.64aee0c6de416; path=/; expires=Mon, 16-Mar-26 10:02:11 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=90", "Content-Type": "text/html", "Server": "nginx", "Set-Cookie": "MPTrack=2f82f324.64aeea622681c; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=c0e09dd1.64aeea622681c; path=/; expires=Mon, 16-Mar-26 10:45:10 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=63bc3bf5.64aee0c73d95a; path=/; expires=Mon, 16-Mar-26 10:02:11 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=99c3917f.64aeea62861b0; path=/; expires=Mon, 16-Mar-26 10:45:10 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=63bc3bf5.64aee0c73d95a; path=/; expires=Mon, 16-Mar-26 10:02:11 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=99c3917f.64aeea62861b0; path=/; expires=Mon, 16-Mar-26 10:45:10 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=63bc3bf5.64aee0c73d95a; path=/; expires=Mon, 16-Mar-26 10:02:11 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=99c3917f.64aeea62861b0; path=/; expires=Mon, 16-Mar-26 10:45:10 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=1d353cac.64aee0c4e7b1e; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=21395cfb.64aee0c4e7b1e; path=/; expires=Mon, 16-Mar-26 10:02:09 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=74b83a9.64aeea602254e; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=4b4e1fae.64aeea602254e; path=/; expires=Mon, 16-Mar-26 10:45:08 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
         <v>8725</v>
       </c>
       <c r="C2" t="n">
-        <v>20260216130205</v>
+        <v>20260216134505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=2b1b810a.64aee0c55331f; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=1fd63542.64aee0c55331f; path=/; expires=Mon, 16-Mar-26 10:02:09 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=259f97d4.64aeea6088580; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=628fcfaf.64aeea6088580; path=/; expires=Mon, 16-Mar-26 10:45:08 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>431</v>
+        <v>379</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=2985c83d.64aee0c5babea; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=2c73919a.64aee0c5babea; path=/; expires=Mon, 16-Mar-26 10:02:10 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=37c8710c.64aeea60eba24; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=ca66587d.64aeea60eba24; path=/; expires=Mon, 16-Mar-26 10:45:08 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>752</v>
+        <v>883</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=1e328659.64aee0c62194b; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=56d41ddb.64aee0c62194b; path=/; expires=Mon, 16-Mar-26 10:02:10 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=5e063122.64aeea614d052; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=aefc4b8.64aeea614d052; path=/; expires=Mon, 16-Mar-26 10:45:09 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>

--- a/data/curated/moex/endpoints_probe/20260216/RU0002868001.xlsx
+++ b/data/curated/moex/endpoints_probe/20260216/RU0002868001.xlsx
@@ -25,9 +25,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondization_amort" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondization_offers_summary" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondization_offers" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meta" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary_all" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meta" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'marketdata'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'history'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'trades'!$A$1:$E$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -556,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>768</v>
+        <v>362</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -600,7 +605,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=f1fffdaf.64aeea5ef59b2; path=/; expires=Mon, 16-Mar-26 10:45:06 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=746181c5.64aeefa97dca3; path=/; expires=Mon, 16-Mar-26 11:08:47 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -655,7 +660,7 @@
         <v>8725</v>
       </c>
       <c r="C2" t="n">
-        <v>20260216134505</v>
+        <v>20260216140845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -669,6 +674,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -792,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>403</v>
+        <v>376</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -848,7 +854,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=90", "Content-Type": "text/html", "Server": "nginx", "Set-Cookie": "MPTrack=2f82f324.64aeea622681c; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=c0e09dd1.64aeea622681c; path=/; expires=Mon, 16-Mar-26 10:45:10 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=90", "Content-Type": "text/html", "Server": "nginx", "Set-Cookie": "MPTrack=61580eaa.64aeefac0c330; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=5fd7468a.64aeefac0c330; path=/; expires=Mon, 16-Mar-26 11:08:49 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -989,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1033,7 +1039,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=99c3917f.64aeea62861b0; path=/; expires=Mon, 16-Mar-26 10:45:10 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=d99409f5.64aeefac67151; path=/; expires=Mon, 16-Mar-26 11:08:50 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1218,7 +1224,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=99c3917f.64aeea62861b0; path=/; expires=Mon, 16-Mar-26 10:45:10 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=d99409f5.64aeefac67151; path=/; expires=Mon, 16-Mar-26 11:08:50 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1403,7 +1409,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=99c3917f.64aeea62861b0; path=/; expires=Mon, 16-Mar-26 10:45:10 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=d99409f5.64aeefac67151; path=/; expires=Mon, 16-Mar-26 11:08:50 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1431,81 +1437,361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>isin</t>
+          <t>endpoint</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>board</t>
+          <t>__status</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>run_date</t>
+          <t>http_status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>endpoints_ok</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>endpoints_failed</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>orderbook_status</t>
+          <t>error</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>source_snapshot</t>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>from_cache</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>elapsed_ms</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RU0002868001</t>
+          <t>securities</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TQCB</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20260216</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>securities,marketdata,history,candles,trades,bondization</t>
-        </is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>orderbook=HTML_INSTEAD_OF_JSON</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>blocked_html</t>
-        </is>
-      </c>
+          <t>empty_table</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>data\curated\moex\bond_rates_20260215.parquet</t>
-        </is>
+          <t>application/json; charset=utf-8</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>application/json; charset=utf-8</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>application/json; charset=utf-8</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>candles</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>empty_table</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>application/json; charset=utf-8</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>trades</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>application/json; charset=utf-8</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>orderbook</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BLOCKED_HTML</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>html_instead_of_json</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>HTML_INSTEAD_OF_JSON</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>text/html</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bondization_coupons</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>empty_table</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>application/json; charset=utf-8</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bondization_amort</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>200</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>empty_table</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>application/json; charset=utf-8</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bondization_offers</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>200</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>empty_table</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>application/json; charset=utf-8</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -1526,6 +1812,94 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>isin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>board</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>run_date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>endpoints_ok</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>endpoints_failed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>orderbook_status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>source_snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RU0002868001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TQCB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>20260216</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>securities,marketdata,history,candles,trades,bondization</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>orderbook=HTML_INSTEAD_OF_JSON</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>blocked_html</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>data\curated\moex\bond_rates_20260215.parquet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1641,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>429</v>
+        <v>386</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1685,7 +2059,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=74b83a9.64aeea602254e; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=4b4e1fae.64aeea602254e; path=/; expires=Mon, 16-Mar-26 10:45:08 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=f7d4e0c.64aeefaa35719; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=30f53284.64aeefaa35719; path=/; expires=Mon, 16-Mar-26 11:08:47 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1740,7 +2114,7 @@
         <v>8725</v>
       </c>
       <c r="C2" t="n">
-        <v>20260216134505</v>
+        <v>20260216140845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1754,6 +2128,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1873,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1917,7 +2292,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=259f97d4.64aeea6088580; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=628fcfaf.64aeea6088580; path=/; expires=Mon, 16-Mar-26 10:45:08 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=67d422f3.64aeefaa96975; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=2385dfd0.64aeefaa96975; path=/; expires=Mon, 16-Mar-26 11:08:48 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1974,6 +2349,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2097,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2141,7 +2517,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=37c8710c.64aeea60eba24; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=ca66587d.64aeea60eba24; path=/; expires=Mon, 16-Mar-26 10:45:08 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=4f11078e.64aeefaaf1ec9; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=aafa08f1.64aeefaaf1ec9; path=/; expires=Mon, 16-Mar-26 11:08:48 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>883</v>
+        <v>767</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2322,7 +2698,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=5e063122.64aeea614d052; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=aefc4b8.64aeea614d052; path=/; expires=Mon, 16-Mar-26 10:45:09 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=6e31771a.64aeefab4dfbd; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=e3be36cf.64aeefab4dfbd; path=/; expires=Mon, 16-Mar-26 11:08:49 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>

--- a/data/curated/moex/endpoints_probe/20260216/RU0002868001.xlsx
+++ b/data/curated/moex/endpoints_probe/20260216/RU0002868001.xlsx
@@ -10,13 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="securities_summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="securities" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marketdata_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marketdata" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marketdata__dataversion" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history__history.cursor" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="candles_summary" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="candles" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trades_summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trades" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trades__dataversion" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orderbook_summary" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orderbook" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondization_coupons_summary" sheetId="13" state="visible" r:id="rId13"/>
@@ -29,9 +29,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="meta" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'marketdata'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'history'!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'trades'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'marketdata__dataversion'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'history__history.cursor'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'trades__dataversion'!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,45 +494,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_meta</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>board</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>params_from</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>params_till</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>params</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_head</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>final_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>headers_subset</t>
         </is>
@@ -561,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -573,39 +588,48 @@
           <t>{"boards": 0, "description": 0}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU0002868001.json</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=746181c5.64aeefa97dca3; path=/; expires=Mon, 16-Mar-26 11:08:47 GMT; domain=.moex.com"}</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=3a56cee8.64aef640565d0; path=/; expires=Mon, 16-Mar-26 11:38:15 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -660,7 +684,7 @@
         <v>8725</v>
       </c>
       <c r="C2" t="n">
-        <v>20260216140845</v>
+        <v>20260216143815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -685,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,45 +755,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_meta</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>board</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>params_from</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>params_till</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>params</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_head</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>final_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>headers_subset</t>
         </is>
@@ -798,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -806,35 +845,44 @@
           <t>{}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>HTML_INSTEAD_OF_JSON</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;!DOCTYPE html&gt;
 &lt;html lang="en" xmlns="http://www.w3.org/1999/xhtml"&gt;
@@ -847,14 +895,14 @@
       </t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boards/TQCB/securities/RU0002868001/orderbook.json</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Cache-Control": "max-age=90", "Content-Type": "text/html", "Server": "nginx", "Set-Cookie": "MPTrack=61580eaa.64aeefac0c330; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=5fd7468a.64aeefac0c330; path=/; expires=Mon, 16-Mar-26 11:08:49 GMT; domain=.moex.com"}</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{"Cache-Control": "max-age=90", "Content-Type": "text/html", "Server": "nginx", "Set-Cookie": "MPTrack=1928504e.64aef642f2587; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=7e65eef5.64aef642f2587; path=/; expires=Mon, 16-Mar-26 11:38:18 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -882,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,45 +976,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_meta</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>board</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>params_from</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>params_till</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>params</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_head</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>final_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>headers_subset</t>
         </is>
@@ -995,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1007,39 +1070,48 @@
           <t>{"amortizations": 0, "coupons": 0, "offers": 0}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>{"from": "2026-01-17", "iss.meta": "off", "iss.only": "coupons,amortizations,offers"}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/statistics/engines/stock/markets/bonds/bondization/RU0002868001.json?from=2026-01-17&amp;iss.only=coupons%2Camortizations%2Coffers&amp;iss.meta=off</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=d99409f5.64aeefac67151; path=/; expires=Mon, 16-Mar-26 11:08:50 GMT; domain=.moex.com"}</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=cb2a9565.64aef6434e905; path=/; expires=Mon, 16-Mar-26 11:38:19 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,45 +1185,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_meta</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>board</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>params_from</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>params_till</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>params</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_head</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>final_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>headers_subset</t>
         </is>
@@ -1180,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1192,39 +1279,48 @@
           <t>{"amortizations": 0, "coupons": 0, "offers": 0}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>{"from": "2026-01-17", "iss.meta": "off", "iss.only": "coupons,amortizations,offers"}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/statistics/engines/stock/markets/bonds/bondization/RU0002868001.json?from=2026-01-17&amp;iss.only=coupons%2Camortizations%2Coffers&amp;iss.meta=off</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=d99409f5.64aeefac67151; path=/; expires=Mon, 16-Mar-26 11:08:50 GMT; domain=.moex.com"}</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=cb2a9565.64aef6434e905; path=/; expires=Mon, 16-Mar-26 11:38:19 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,45 +1394,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_meta</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>board</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>params_from</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>params_till</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>params</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_head</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>final_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>headers_subset</t>
         </is>
@@ -1365,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1377,39 +1488,48 @@
           <t>{"amortizations": 0, "coupons": 0, "offers": 0}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>{"from": "2026-01-17", "iss.meta": "off", "iss.only": "coupons,amortizations,offers"}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/statistics/engines/stock/markets/bonds/bondization/RU0002868001.json?from=2026-01-17&amp;iss.only=coupons%2Camortizations%2Coffers&amp;iss.meta=off</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=d99409f5.64aeefac67151; path=/; expires=Mon, 16-Mar-26 11:08:50 GMT; domain=.moex.com"}</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=cb2a9565.64aef6434e905; path=/; expires=Mon, 16-Mar-26 11:38:19 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,30 +1578,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>content_type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>from_cache</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>elapsed_ms</t>
         </is>
@@ -1504,22 +1634,28 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>empty_table</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>application/json; charset=utf-8</t>
         </is>
       </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>362</v>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="3">
@@ -1530,7 +1666,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1539,18 +1675,28 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>only_meta_tables</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>application/json; charset=utf-8</t>
         </is>
       </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>386</v>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>399</v>
       </c>
     </row>
     <row r="4">
@@ -1570,18 +1716,24 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>application/json; charset=utf-8</t>
         </is>
       </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>381</v>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>392</v>
       </c>
     </row>
     <row r="5">
@@ -1601,22 +1753,28 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>empty_table</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>application/json; charset=utf-8</t>
         </is>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>367</v>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>412</v>
       </c>
     </row>
     <row r="6">
@@ -1627,7 +1785,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO_DATA</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1636,18 +1794,28 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>only_meta_tables</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>application/json; charset=utf-8</t>
         </is>
       </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>767</v>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>751</v>
       </c>
     </row>
     <row r="7">
@@ -1667,26 +1835,32 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>html_instead_of_json</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>HTML_INSTEAD_OF_JSON</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>text/html</t>
         </is>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>376</v>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>366</v>
       </c>
     </row>
     <row r="8">
@@ -1706,22 +1880,28 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>empty_table</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>application/json; charset=utf-8</t>
         </is>
       </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>381</v>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -1741,22 +1921,28 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>empty_table</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>application/json; charset=utf-8</t>
         </is>
       </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>381</v>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1776,22 +1962,28 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>empty_table</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>application/json; charset=utf-8</t>
         </is>
       </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>381</v>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -1906,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,45 +2144,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_meta</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>board</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>params_from</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>params_till</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>params</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_head</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>final_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>headers_subset</t>
         </is>
@@ -1999,10 +2206,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>only_meta_tables</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>200</v>
       </c>
@@ -2015,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2027,39 +2238,48 @@
           <t>{"dataversion": 1, "marketdata": 0, "marketdata_yields": 0, "securities": 0}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boards/TQCB/securities/RU0002868001.json</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=f7d4e0c.64aeefaa35719; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=30f53284.64aeefaa35719; path=/; expires=Mon, 16-Mar-26 11:08:47 GMT; domain=.moex.com"}</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=f8a6ab9.64aef6410e782; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=9c8c70ac.64aef6410e782; path=/; expires=Mon, 16-Mar-26 11:38:16 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2334,7 @@
         <v>8725</v>
       </c>
       <c r="C2" t="n">
-        <v>20260216140845</v>
+        <v>20260216143815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2139,7 +2359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2185,45 +2405,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_meta</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>board</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>params_from</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>params_till</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>params</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_head</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>final_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>headers_subset</t>
         </is>
@@ -2248,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2260,39 +2495,48 @@
           <t>{"history": 0, "history.cursor": 1}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>{"from": "2026-01-17", "till": "2026-02-16"}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/history/engines/stock/markets/bonds/boards/TQCB/securities/RU0002868001.json?from=2026-01-17&amp;till=2026-02-16</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=67d422f3.64aeefaa96975; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=2385dfd0.64aeefaa96975; path=/; expires=Mon, 16-Mar-26 11:08:48 GMT; domain=.moex.com"}</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=5eb96d9e.64aef64174553; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=c715e120.64aef64174553; path=/; expires=Mon, 16-Mar-26 11:38:17 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2406,45 +2650,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_meta</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>board</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>params_from</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>params_till</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>params</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_head</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>final_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>headers_subset</t>
         </is>
@@ -2473,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>367</v>
+        <v>412</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2485,39 +2744,48 @@
           <t>{"candles": 0}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>{"from": "2026-01-17", "interval": 24, "till": "2026-02-16"}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boards/TQCB/securities/RU0002868001/candles.json?from=2026-01-17&amp;till=2026-02-16&amp;interval=24</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=4f11078e.64aeefaaf1ec9; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=aafa08f1.64aeefaaf1ec9; path=/; expires=Mon, 16-Mar-26 11:08:48 GMT; domain=.moex.com"}</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=7cc141c9.64aef641ddfc4; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=3026e4eb.64aef641ddfc4; path=/; expires=Mon, 16-Mar-26 11:38:17 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2591,45 +2859,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>rows_total</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rows_meta</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rows_effective</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>board</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>params_from</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>params_till</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>params</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_head</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>final_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>headers_subset</t>
         </is>
@@ -2638,10 +2921,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>only_meta_tables</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>200</v>
       </c>
@@ -2654,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2666,39 +2953,48 @@
           <t>{"dataversion": 1, "trades": 0, "trades_yields": 0}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01-17</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>{"from": "2026-01-17", "till": "2026-02-16"}</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/boards/TQCB/securities/RU0002868001/trades.json?from=2026-01-17&amp;till=2026-02-16</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=6e31771a.64aeefab4dfbd; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=e3be36cf.64aeefab4dfbd; path=/; expires=Mon, 16-Mar-26 11:08:49 GMT; domain=.moex.com"}</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=5fcded21.64aef6423ef0b; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=cb513479.64aef6423ef0b; path=/; expires=Mon, 16-Mar-26 11:38:17 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>

--- a/data/curated/moex/endpoints_probe/20260216/RU0002868001.xlsx
+++ b/data/curated/moex/endpoints_probe/20260216/RU0002868001.xlsx
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=3a56cee8.64aef640565d0; path=/; expires=Mon, 16-Mar-26 11:38:15 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=1d77b65f.64aefa9b3786f; path=/; expires=Mon, 16-Mar-26 11:57:45 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
         <v>8725</v>
       </c>
       <c r="C2" t="n">
-        <v>20260216143815</v>
+        <v>20260216145745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=90", "Content-Type": "text/html", "Server": "nginx", "Set-Cookie": "MPTrack=1928504e.64aef642f2587; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=7e65eef5.64aef642f2587; path=/; expires=Mon, 16-Mar-26 11:38:18 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=90", "Content-Type": "text/html", "Server": "nginx", "Set-Cookie": "MPTrack=3fe6d70e.64aefa9db7d4f; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=c9093dd0.64aefa9db7d4f; path=/; expires=Mon, 16-Mar-26 11:57:47 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=cb2a9565.64aef6434e905; path=/; expires=Mon, 16-Mar-26 11:38:19 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=a57d8cf7.64aefa9e101d4; path=/; expires=Mon, 16-Mar-26 11:57:47 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=cb2a9565.64aef6434e905; path=/; expires=Mon, 16-Mar-26 11:38:19 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=a57d8cf7.64aefa9e101d4; path=/; expires=Mon, 16-Mar-26 11:57:47 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=cb2a9565.64aef6434e905; path=/; expires=Mon, 16-Mar-26 11:38:19 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MicexTrackID=a57d8cf7.64aefa9e101d4; path=/; expires=Mon, 16-Mar-26 11:57:47 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>350</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3">
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>399</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4">
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5">
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>412</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>751</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7">
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>366</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8">
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -2226,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=f8a6ab9.64aef6410e782; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=9c8c70ac.64aef6410e782; path=/; expires=Mon, 16-Mar-26 11:38:16 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=6b01b44d.64aefa9bee8d4; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=62ecade3.64aefa9bee8d4; path=/; expires=Mon, 16-Mar-26 11:57:45 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
         <v>8725</v>
       </c>
       <c r="C2" t="n">
-        <v>20260216143815</v>
+        <v>20260216145740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=5eb96d9e.64aef64174553; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=c715e120.64aef64174553; path=/; expires=Mon, 16-Mar-26 11:38:17 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=2bba72d4.64aefa9c505cb; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=94e9db77.64aefa9c505cb; path=/; expires=Mon, 16-Mar-26 11:57:46 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>412</v>
+        <v>365</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=7cc141c9.64aef641ddfc4; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=3026e4eb.64aef641ddfc4; path=/; expires=Mon, 16-Mar-26 11:38:17 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=288485a1.64aefa9cadaa3; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=4d612c27.64aefa9cadaa3; path=/; expires=Mon, 16-Mar-26 11:57:46 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>751</v>
+        <v>719</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=5fcded21.64aef6423ef0b; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=cb513479.64aef6423ef0b; path=/; expires=Mon, 16-Mar-26 11:38:17 GMT; domain=.moex.com"}</t>
+          <t>{"Cache-Control": "max-age=5", "Content-Type": "application/json; charset=utf-8", "Server": "nginx", "Set-Cookie": "MPTrack=773f2577.64aefa9d059bd; path=/; domain=.moex.com; Secure; HttpOnly, MicexTrackID=427e2867.64aefa9d059bd; path=/; expires=Mon, 16-Mar-26 11:57:46 GMT; domain=.moex.com"}</t>
         </is>
       </c>
     </row>
